--- a/runs/runs/AB_Runs/AB_replicating_DW2_14/Vial Loadings.xlsx
+++ b/runs/runs/AB_Runs/AB_replicating_DW2_14/Vial Loadings.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mitprod-my.sharepoint.com/personal/alexb22_mit_edu/Documents/Documents/Automated Synthesis/Alex Runs/DW-2.14 Replication/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mitprod-my.sharepoint.com/personal/alexb22_mit_edu/Documents/Documents/Automated Synthesis/Automated-Synthesis-Alex-B-/runs/runs/AB_Runs/AB_replicating_DW2_14/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F402B9D9-3956-4204-B9D6-DAD55111438E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="8_{F402B9D9-3956-4204-B9D6-DAD55111438E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38607F2B-A244-4F4C-8205-2506B31DE68D}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{1F3E78CA-97B2-419F-9C34-2FF7701E1DFB}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -475,6 +474,7 @@
         <v>1.8010460251046025</v>
       </c>
       <c r="E2">
+        <f>200*E3</f>
         <v>2</v>
       </c>
     </row>
@@ -502,11 +502,11 @@
       </c>
       <c r="D4">
         <f>E4*(A11/1000)*B4*1000</f>
-        <v>1.3562000000000003</v>
+        <v>8.1372000000000018</v>
       </c>
       <c r="E4">
-        <f>0.02*E3</f>
-        <v>2.0000000000000001E-4</v>
+        <f>(6*(10^-4))*E2</f>
+        <v>1.2000000000000001E-3</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
